--- a/artfynd/A 64239-2021 artfynd.xlsx
+++ b/artfynd/A 64239-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64239-2021 artfynd.xlsx
+++ b/artfynd/A 64239-2021 artfynd.xlsx
@@ -2537,7 +2537,7 @@
         <v>130435051</v>
       </c>
       <c r="B18" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 64239-2021 artfynd.xlsx
+++ b/artfynd/A 64239-2021 artfynd.xlsx
@@ -2537,7 +2537,7 @@
         <v>130435051</v>
       </c>
       <c r="B18" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 64239-2021 artfynd.xlsx
+++ b/artfynd/A 64239-2021 artfynd.xlsx
@@ -2537,7 +2537,7 @@
         <v>130435051</v>
       </c>
       <c r="B18" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 64239-2021 artfynd.xlsx
+++ b/artfynd/A 64239-2021 artfynd.xlsx
@@ -2537,7 +2537,7 @@
         <v>130435051</v>
       </c>
       <c r="B18" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 64239-2021 artfynd.xlsx
+++ b/artfynd/A 64239-2021 artfynd.xlsx
@@ -2537,7 +2537,7 @@
         <v>130435051</v>
       </c>
       <c r="B18" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 64239-2021 artfynd.xlsx
+++ b/artfynd/A 64239-2021 artfynd.xlsx
@@ -2537,7 +2537,7 @@
         <v>130435051</v>
       </c>
       <c r="B18" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 64239-2021 artfynd.xlsx
+++ b/artfynd/A 64239-2021 artfynd.xlsx
@@ -2537,7 +2537,7 @@
         <v>130435051</v>
       </c>
       <c r="B18" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 64239-2021 artfynd.xlsx
+++ b/artfynd/A 64239-2021 artfynd.xlsx
@@ -2537,7 +2537,7 @@
         <v>130435051</v>
       </c>
       <c r="B18" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 64239-2021 artfynd.xlsx
+++ b/artfynd/A 64239-2021 artfynd.xlsx
@@ -2537,7 +2537,7 @@
         <v>130435051</v>
       </c>
       <c r="B18" t="n">
-        <v>91776</v>
+        <v>91784</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 64239-2021 artfynd.xlsx
+++ b/artfynd/A 64239-2021 artfynd.xlsx
@@ -2537,7 +2537,7 @@
         <v>130435051</v>
       </c>
       <c r="B18" t="n">
-        <v>91784</v>
+        <v>91798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 64239-2021 artfynd.xlsx
+++ b/artfynd/A 64239-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75200047</v>
+        <v>106607544</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Väfjället Ö, Jmt</t>
+          <t>Blötmon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>405243.815541066</v>
+        <v>405381</v>
       </c>
       <c r="R2" t="n">
-        <v>7023664.953867411</v>
+        <v>7023914</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-12-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-12-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,62 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall, Andreas Johnsen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75200049</v>
+        <v>130435051</v>
       </c>
       <c r="B3" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Väfjället Ö, Jmt</t>
+          <t>Väfjället, Väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>405250.8236957884</v>
+        <v>405244</v>
       </c>
       <c r="R3" t="n">
-        <v>7023627.885832503</v>
+        <v>7023678</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,27 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-12-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-12-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Nencia Mattsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johan Råghall, Andreas Johnsen</t>
+          <t>Nencia Mattsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -907,16 +872,11 @@
         <v>75200051</v>
       </c>
       <c r="B4" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -944,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>405250.0403920931</v>
+        <v>405250</v>
       </c>
       <c r="R4" t="n">
-        <v>7023586.102515888</v>
+        <v>7023586</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,19 +937,9 @@
           <t>2018-12-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-12-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,53 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91846294</v>
+        <v>75200049</v>
       </c>
       <c r="B5" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>1249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Väfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>405338.1540469945</v>
+        <v>405251</v>
       </c>
       <c r="R5" t="n">
-        <v>7023933.221161708</v>
+        <v>7023628</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,22 +1031,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-12-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-12-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,70 +1056,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Johan Råghall, Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98677520</v>
+        <v>128484686</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öster om väfjället, Jmt</t>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>405698.3343474483</v>
+        <v>405413</v>
       </c>
       <c r="R6" t="n">
-        <v>7024227.802171786</v>
+        <v>7024030</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,22 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-02-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-02-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,70 +1149,69 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Brant, örtrik grannaturskog ner mot bäckmiljö</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98677522</v>
+        <v>75200047</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öster om väfjället, Jmt</t>
+          <t>Väfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>405698.3343474483</v>
+        <v>405244</v>
       </c>
       <c r="R7" t="n">
-        <v>7024227.802171786</v>
+        <v>7023665</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1316,22 +1235,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-02-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2018-12-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-02-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:46</t>
+          <t>2018-12-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,27 +1255,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Oskar Kullingsjö</t>
+          <t>Johan Råghall, Andreas Johnsen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99109084</v>
+        <v>98677520</v>
       </c>
       <c r="B8" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,19 +1296,17 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Väfjället Ö, Jmt</t>
+          <t>Öster om väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>405532.1064589866</v>
+        <v>405698</v>
       </c>
       <c r="R8" t="n">
-        <v>7024100.103475161</v>
+        <v>7024228</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1431,22 +1333,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2022-02-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-03-12</t>
+          <t>2022-02-19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,34 +1357,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Andreas Johnsen</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Johnsen</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99108983</v>
+        <v>99108810</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1517,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>405469.7060604398</v>
+        <v>405377</v>
       </c>
       <c r="R9" t="n">
-        <v>7023983.2812453</v>
+        <v>7023613</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,24 +1446,9 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,15 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99108833</v>
+        <v>99108864</v>
       </c>
       <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1611,21 +1487,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1638,10 +1514,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>405421.2145372985</v>
+        <v>405443</v>
       </c>
       <c r="R10" t="n">
-        <v>7023788.731890203</v>
+        <v>7023932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,19 +1547,9 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,15 +1577,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99108902</v>
+        <v>99108889</v>
       </c>
       <c r="B11" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1727,21 +1588,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1754,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>405370.373854079</v>
+        <v>405421</v>
       </c>
       <c r="R11" t="n">
-        <v>7023926.877126235</v>
+        <v>7023959</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,19 +1648,9 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,15 +1678,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>99108889</v>
+        <v>99108941</v>
       </c>
       <c r="B12" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1870,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>405421.270536638</v>
+        <v>405372</v>
       </c>
       <c r="R12" t="n">
-        <v>7023958.638538139</v>
+        <v>7023949</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,19 +1749,14 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,15 +1784,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>99108864</v>
+        <v>99108983</v>
       </c>
       <c r="B13" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>405443.4378195282</v>
+        <v>405470</v>
       </c>
       <c r="R13" t="n">
-        <v>7023931.915328087</v>
+        <v>7023983</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,19 +1855,14 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,15 +1890,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>99108941</v>
+        <v>99109084</v>
       </c>
       <c r="B14" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2102,13 +1928,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>405372.3718261836</v>
+        <v>405532</v>
       </c>
       <c r="R14" t="n">
-        <v>7023948.842947808</v>
+        <v>7024100</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2135,24 +1961,9 @@
           <t>2022-03-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-03-12</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2180,15 +1991,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>106607546</v>
+        <v>128484529</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,38 +2002,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Blötmon, Jmt</t>
+          <t>Bustadbäcken, Bustadbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>405410.5164101804</v>
+        <v>405543</v>
       </c>
       <c r="R15" t="n">
-        <v>7023914.456557103</v>
+        <v>7024164</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,27 +2056,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,70 +2072,69 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>106607547</v>
+        <v>99108965</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Blötmon, Jmt</t>
+          <t>Väfjället Ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>405440.1312987657</v>
+        <v>405372</v>
       </c>
       <c r="R16" t="n">
-        <v>7023941.901396893</v>
+        <v>7024003</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,27 +2161,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2022-03-12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,71 +2175,68 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Andreas Johnsen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Andreas Johnsen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>106607544</v>
+        <v>98677522</v>
       </c>
       <c r="B17" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Blötmon, Jmt</t>
+          <t>Öster om väfjället, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>405380.7960385594</v>
+        <v>405698</v>
       </c>
       <c r="R17" t="n">
-        <v>7023913.984202239</v>
+        <v>7024228</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2492,22 +2260,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
+          <t>2022-02-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
+          <t>2022-02-19</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2522,22 +2290,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Oskar Kullingsjö</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130435051</v>
+        <v>106607546</v>
       </c>
       <c r="B18" t="n">
-        <v>91798</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2545,34 +2313,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väfjället, Väfjället, Jmt</t>
+          <t>Blötmon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>405244</v>
+        <v>405411</v>
       </c>
       <c r="R18" t="n">
-        <v>7023678</v>
+        <v>7023915</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2599,12 +2371,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2023-02-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2619,15 +2396,324 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Nencia Mattsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>106607547</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Blötmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>405440</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7023942</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-02-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>91846294</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>405338</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7023933</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>72971800</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Väfjället Ö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>405515</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7023751</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2018-06-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2018-06-03</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Andreas Johnsen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64239-2021 artfynd.xlsx
+++ b/artfynd/A 64239-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106607544</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130435051</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75200051</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75200049</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484686</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75200047</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1372,6 +1407,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98677520</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99108810</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1574,6 +1619,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99108864</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1675,6 +1725,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99108889</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1781,6 +1836,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99108941</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1887,6 +1947,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99108983</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1988,6 +2053,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99109084</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2090,6 +2160,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128484529</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2191,6 +2266,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99108965</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2299,6 +2379,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98677522</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2405,6 +2490,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106607546</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2511,6 +2601,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106607547</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2610,6 +2705,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91846294</t>
         </is>
       </c>
     </row>
@@ -2714,8 +2814,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72971800</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>